--- a/output/pdf_financials_xlsx/ZTE.xlsx
+++ b/output/pdf_financials_xlsx/ZTE.xlsx
@@ -630,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.020148</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.128579</v>
       </c>
     </row>
     <row r="13">
@@ -884,10 +884,10 @@
         <v>0.366591</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.872629</v>
+        <v>3.852481</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.423336</v>
+        <v>2.294757</v>
       </c>
     </row>
     <row r="28">
@@ -916,10 +916,10 @@
         <v>0.366591</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.872629</v>
+        <v>3.852481</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.423336</v>
+        <v>2.294757</v>
       </c>
     </row>
     <row r="30">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZTE.xlsx
+++ b/output/pdf_financials_xlsx/ZTE.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.165775</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.165775</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.165774</v>
       </c>
     </row>
     <row r="29">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.366591</v>
+        <v>0.532366</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.852481</v>
+        <v>4.018256</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.294757</v>
+        <v>2.460531</v>
       </c>
     </row>
     <row r="30">
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.165775</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.165775</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.165774</v>
       </c>
     </row>
     <row r="101">
@@ -3556,7 +3556,11 @@
           <t>Depreciation of right of use asset</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.165775</v>
       </c>

--- a/output/pdf_financials_xlsx/ZTE.xlsx
+++ b/output/pdf_financials_xlsx/ZTE.xlsx
@@ -2258,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.68737</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.052787</v>
       </c>
     </row>
     <row r="112">
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.078073</v>
       </c>
     </row>
     <row r="122">
@@ -2638,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.68737</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.052787</v>
       </c>
     </row>
     <row r="135">
@@ -3941,7 +3941,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4059,7 +4063,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4088,7 +4096,11 @@
           <t>Normal course issuer bid share repurchases</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
